--- a/data.xlsx
+++ b/data.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>EO 멸균 공정 밸리데이션 절차서</t>
+          <t>EO 멸균 공정 밸리데이션 절차서 (QP-757-01)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>완제품 검사성적서</t>
+          <t>완제품 검사성적서 (QP-757-01-F01)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>공정검사지침서</t>
+          <t>공정검사지침서 (QP-757-01-F02)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>바이오 버든 선정 가이드</t>
+          <t>바이오 버든 선정 가이드 (QP-757-01-F03)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -606,7 +606,11 @@
           <t>위험관리 절차서 (QP-71-01)</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>001. 위험 관리/001. 절차서/QP-71-01_위험관리_절차서.pdf</t>
+        </is>
+      </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
           <t>001. 위험 관리/001. 절차서/QP-71-01_위험관리_절차서.docx</t>
@@ -656,7 +660,11 @@
           <t>위험관리 보고서 (QP-71-01-F02)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>001. 위험 관리/002. 관련 양식/002. 위험관리 보고서/QP-71-01-F02_위험관리_보고서.pdf</t>
+        </is>
+      </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
           <t>001. 위험 관리/002. 관련 양식/002. 위험관리 보고서/QP-71-01-F02_위험관리_보고서.docx</t>
@@ -679,7 +687,11 @@
           <t>제조공정 FMEA (QP-71-F03)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>001. 위험 관리/002. 관련 양식/003. 위험관리 제조공정 FMEA/QP-71-F03_제조공정_FMEA.pdf</t>
+        </is>
+      </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
           <t>001. 위험 관리/002. 관련 양식/003. 위험관리 제조공정 FMEA/QP-71-F03_제조공정_FMEA_수정본.docx</t>
@@ -702,7 +714,11 @@
           <t>공급업체 관리 절차서 (QP-74-01)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>002. 공급업체 관리/001. 절차서/QP-74-01_공급업체_관리_절차서.pdf</t>
+        </is>
+      </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
           <t>002. 공급업체 관리/001. 절차서/QP-74-01_공급업체_관리_절차서.docx</t>
@@ -725,7 +741,11 @@
           <t>공급업체 등록 및 평가서 (QP-74-01-F01)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>002. 공급업체 관리/002. 관련 양식/001. 공급업체 등록 및 평가서/QP-74-01-F01_공급업체_등록_및_평가서__1_.pdf</t>
+        </is>
+      </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
           <t>002. 공급업체 관리/002. 관련 양식/001. 공급업체 등록 및 평가서/QP-74-01-F01_공급업체_등록_및_평가서 (1).docx</t>
@@ -748,7 +768,11 @@
           <t>승인 공급업체 관리 대장 (QP-74-01-F02)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>002. 공급업체 관리/002. 관련 양식/002. 승인 공급 업체 관리대장/QP-74-01-F02_승인_공급업체_관리_대장.pdf</t>
+        </is>
+      </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
           <t>002. 공급업체 관리/002. 관련 양식/002. 승인 공급 업체 관리대장/QP-74-01-F02_승인_공급업체_관리_대장.docx</t>
@@ -771,7 +795,7 @@
           <t>공급업체 관리 절차서 발표 (QP-74-01)</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="inlineStr">
         <is>
           <t>002. 공급업체 관리/005. 발표 영상/001. 절차서/QP-74-01 공급업체 관리 절차서 발표.mp4</t>
@@ -794,7 +818,11 @@
           <t>EO 멸균 공정 밸리데이션 절차서 (QP-757-01)</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>003. 멸균 공정 밸리데이션/001. 절차서 양식/EO_멸균_공정_밸리데이션_절차서.pdf</t>
+        </is>
+      </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
           <t>003. 멸균 공정 밸리데이션/001. 절차서 양식/EO_멸균_공정_밸리데이션_절차서.docx</t>
@@ -844,7 +872,11 @@
           <t>공정검사지침서 (QP-757-01-F02)</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/002. 공정검사지침서/공정검사지침서.pdf</t>
+        </is>
+      </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
           <t>003. 멸균 공정 밸리데이션/002. 관련 양식/002. 공정검사지침서/공정검사지침서.docx</t>
@@ -867,7 +899,11 @@
           <t>바이오 버든 선정 가이드 (QP-757-01-F03)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/003. 바이오 버든 선정 가이드/바이오 버든 선정 가이드.pdf</t>
+        </is>
+      </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
           <t>003. 멸균 공정 밸리데이션/002. 관련 양식/003. 바이오 버든 선정 가이드/바이오 버든 선정 가이드.docx</t>
@@ -890,7 +926,11 @@
           <t>시정 및 예방조치 절차서 (QP-85-01)</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>004. CAPA 절차/001. 절차서/QP-85-01_시정_및_예방조치_절차서.pdf</t>
+        </is>
+      </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
           <t>004. CAPA 절차/001. 절차서/QP-85-01_시정_및_예방조치_절차서_4차 수정.docx</t>
@@ -913,7 +953,11 @@
           <t>시정 및 예방조치 요구·보고서 (QP-85-01-F01)</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>004. CAPA 절차/002. 관련 양식/001. 시정조치 및 예방조치 요구, 보고서/QP-85-01-F01_시정_및_예방조치_요구_보고서.pdf</t>
+        </is>
+      </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
           <t>004. CAPA 절차/002. 관련 양식/001. 시정조치 및 예방조치 요구, 보고서/QP-85-01-F01_시정_및_예방조치_요구_보고서.docx</t>
@@ -936,7 +980,11 @@
           <t>시정조치 및 예방조치 관리대장 (QP-85-01-F01)</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>004. CAPA 절차/002. 관련 양식/002. 시정조치 및 예방조치 요구, 보고서 관리 대장/QP-85-01-F01_시정조치_및_예방조치_관리대장.pdf</t>
+        </is>
+      </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
           <t>004. CAPA 절차/002. 관련 양식/002. 시정조치 및 예방조치 요구, 보고서 관리 대장/QP-85-01-F01_시정조치_및_예방조치_관리대장.xlsx</t>
@@ -959,7 +1007,11 @@
           <t>부적합 보고서(NCR) 회신</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>004. CAPA 절차/004. 부적합/QP-85-01_부적합보고서_NCR_회신.pdf</t>
+        </is>
+      </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
           <t>004. CAPA 절차/004. 부적합/QP-85-01_부적합보고서_NCR_회신.docx</t>
@@ -982,7 +1034,11 @@
           <t>UDI 절차서 (QP-758-01)</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>005. UDI 관리/001. 절차서/QP-758-01_UDI_절차서.pdf</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
           <t>005. UDI 관리/001. 절차서/QP-758-01_UDI_절차서.docx</t>
@@ -1005,7 +1061,11 @@
           <t>UDI 체계 수립 및 코드 생성 기록 (QP-758-01-F01)</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>005. UDI 관리/002. 관련 양식/001. UDI 체계 수립 및 코드 생성/QP-758-01-F01_UDI체계수립및코드생성기록.pdf</t>
+        </is>
+      </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
           <t>005. UDI 관리/002. 관련 양식/001. UDI 체계 수립 및 코드 생성/QP-758-01-F01_UDI체계수립및코드생성기록.docx</t>
@@ -1055,7 +1115,11 @@
           <t>통합시스템 등록 및 추적관리 (QP-758-01-F03)</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>005. UDI 관리/002. 관련 양식/003. 통합시스템 등록 및 추적관리/QP-758-01-F03_작성예시_KMHSE-02-10.pdf</t>
+        </is>
+      </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
           <t>005. UDI 관리/002. 관련 양식/003. 통합시스템 등록 및 추적관리/QP-758-01-F03_작성예시_KMHSE-02-10.docx</t>

--- a/data.xlsx
+++ b/data.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -701,27 +701,27 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>공급업체 관리</t>
+          <t>위험 관리</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>절차서</t>
+          <t>부적합 사례</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>공급업체 관리 절차서 (QP-74-01)</t>
+          <t>부적합 보고서(NCR) 회신</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>002. 공급업체 관리/001. 절차서/QP-74-01_공급업체_관리_절차서.pdf</t>
+          <t>001. 위험 관리/004. 부적합/QP-71-01_부적합보고서_NCR_회신.pdf</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>002. 공급업체 관리/001. 절차서/QP-74-01_공급업체_관리_절차서.docx</t>
+          <t>001. 위험 관리/004. 부적합/QP-71-01_부적합보고서_NCR_회신.docx</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>양식</t>
+          <t>절차서</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>공급업체 등록 및 평가서 (QP-74-01-F01)</t>
+          <t>공급업체 관리 절차서 (QP-74-01)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>002. 공급업체 관리/002. 관련 양식/001. 공급업체 등록 및 평가서/QP-74-01-F01_공급업체_등록_및_평가서__1_.pdf</t>
+          <t>002. 공급업체 관리/001. 절차서/QP-74-01_공급업체_관리_절차서.pdf</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>002. 공급업체 관리/002. 관련 양식/001. 공급업체 등록 및 평가서/QP-74-01-F01_공급업체_등록_및_평가서 (1).docx</t>
+          <t>002. 공급업체 관리/001. 절차서/QP-74-01_공급업체_관리_절차서.docx</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>승인 공급업체 관리 대장 (QP-74-01-F02)</t>
+          <t>공급업체 등록 및 평가서 (QP-74-01-F01)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>002. 공급업체 관리/002. 관련 양식/002. 승인 공급 업체 관리대장/QP-74-01-F02_승인_공급업체_관리_대장.pdf</t>
+          <t>002. 공급업체 관리/002. 관련 양식/001. 공급업체 등록 및 평가서/QP-74-01-F01_공급업체_등록_및_평가서__1_.pdf</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>002. 공급업체 관리/002. 관련 양식/002. 승인 공급 업체 관리대장/QP-74-01-F02_승인_공급업체_관리_대장.docx</t>
+          <t>002. 공급업체 관리/002. 관련 양식/001. 공급업체 등록 및 평가서/QP-74-01-F01_공급업체_등록_및_평가서 (1).docx</t>
         </is>
       </c>
     </row>
@@ -787,45 +787,45 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>비디오</t>
+          <t>양식</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>공급업체 관리 절차서 발표 (QP-74-01)</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
+          <t>승인 공급업체 관리 대장 (QP-74-01-F02)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>002. 공급업체 관리/002. 관련 양식/002. 승인 공급 업체 관리대장/QP-74-01-F02_승인_공급업체_관리_대장.pdf</t>
+        </is>
+      </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>002. 공급업체 관리/005. 발표 영상/001. 절차서/QP-74-01 공급업체 관리 절차서 발표.mp4</t>
+          <t>002. 공급업체 관리/002. 관련 양식/002. 승인 공급 업체 관리대장/QP-74-01-F02_승인_공급업체_관리_대장.docx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>멸균 공정 밸리데이션</t>
+          <t>공급업체 관리</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>절차서</t>
+          <t>비디오</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>EO 멸균 공정 밸리데이션 절차서 (QP-757-01)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>003. 멸균 공정 밸리데이션/001. 절차서 양식/EO_멸균_공정_밸리데이션_절차서.pdf</t>
-        </is>
-      </c>
+          <t>공급업체 관리 절차서 발표 (QP-74-01)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>003. 멸균 공정 밸리데이션/001. 절차서 양식/EO_멸균_공정_밸리데이션_절차서.docx</t>
+          <t>002. 공급업체 관리/005. 발표 영상/001. 절차서/QP-74-01 공급업체 관리 절차서 발표.mp4</t>
         </is>
       </c>
     </row>
@@ -837,22 +837,22 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>양식</t>
+          <t>절차서</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>완제품 검사성적서 (QP-757-01-F01)</t>
+          <t>EO 멸균 공정 밸리데이션 절차서 (QP-757-01)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/001. 완제품 검사성적서/완제품 검사성적서.pdf</t>
+          <t>003. 멸균 공정 밸리데이션/001. 절차서 양식/EO_멸균_공정_밸리데이션_절차서.pdf</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/001. 완제품 검사성적서/완제품 검사성적서.pdf</t>
+          <t>003. 멸균 공정 밸리데이션/001. 절차서 양식/EO_멸균_공정_밸리데이션_절차서.docx</t>
         </is>
       </c>
     </row>
@@ -869,17 +869,17 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>공정검사지침서 (QP-757-01-F02)</t>
+          <t>완제품 검사성적서 (QP-757-01-F01)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/002. 공정검사지침서/공정검사지침서.pdf</t>
+          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/001. 완제품 검사성적서/완제품 검사성적서.pdf</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/002. 공정검사지침서/공정검사지침서.docx</t>
+          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/001. 완제품 검사성적서/완제품 검사성적서.pdf</t>
         </is>
       </c>
     </row>
@@ -896,44 +896,44 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>바이오 버든 선정 가이드 (QP-757-01-F03)</t>
+          <t>공정검사지침서 (QP-757-01-F02)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/003. 바이오 버든 선정 가이드/바이오 버든 선정 가이드.pdf</t>
+          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/002. 공정검사지침서/공정검사지침서.pdf</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/003. 바이오 버든 선정 가이드/바이오 버든 선정 가이드.docx</t>
+          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/002. 공정검사지침서/공정검사지침서.docx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>CAPA</t>
+          <t>멸균 공정 밸리데이션</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>절차서</t>
+          <t>양식</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>시정 및 예방조치 절차서 (QP-85-01)</t>
+          <t>바이오 버든 선정 가이드 (QP-757-01-F03)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>004. CAPA 절차/001. 절차서/QP-85-01_시정_및_예방조치_절차서.pdf</t>
+          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/003. 바이오 버든 선정 가이드/바이오 버든 선정 가이드.pdf</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>004. CAPA 절차/001. 절차서/QP-85-01_시정_및_예방조치_절차서_4차 수정.docx</t>
+          <t>003. 멸균 공정 밸리데이션/002. 관련 양식/003. 바이오 버든 선정 가이드/바이오 버든 선정 가이드.docx</t>
         </is>
       </c>
     </row>
@@ -945,22 +945,22 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>양식</t>
+          <t>절차서</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>시정 및 예방조치 요구·보고서 (QP-85-01-F01)</t>
+          <t>시정 및 예방조치 절차서 (QP-85-01)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>004. CAPA 절차/002. 관련 양식/001. 시정조치 및 예방조치 요구, 보고서/QP-85-01-F01_시정_및_예방조치_요구_보고서.pdf</t>
+          <t>004. CAPA 절차/001. 절차서/QP-85-01_시정_및_예방조치_절차서.pdf</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>004. CAPA 절차/002. 관련 양식/001. 시정조치 및 예방조치 요구, 보고서/QP-85-01-F01_시정_및_예방조치_요구_보고서.docx</t>
+          <t>004. CAPA 절차/001. 절차서/QP-85-01_시정_및_예방조치_절차서_4차 수정.docx</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>시정조치 및 예방조치 관리대장 (QP-85-01-F01)</t>
+          <t>시정 및 예방조치 요구·보고서 (QP-85-01-F01)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>004. CAPA 절차/002. 관련 양식/002. 시정조치 및 예방조치 요구, 보고서 관리 대장/QP-85-01-F01_시정조치_및_예방조치_관리대장.pdf</t>
+          <t>004. CAPA 절차/002. 관련 양식/001. 시정조치 및 예방조치 요구, 보고서/QP-85-01-F01_시정_및_예방조치_요구_보고서.pdf</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>004. CAPA 절차/002. 관련 양식/002. 시정조치 및 예방조치 요구, 보고서 관리 대장/QP-85-01-F01_시정조치_및_예방조치_관리대장.xlsx</t>
+          <t>004. CAPA 절차/002. 관련 양식/001. 시정조치 및 예방조치 요구, 보고서/QP-85-01-F01_시정_및_예방조치_요구_보고서.docx</t>
         </is>
       </c>
     </row>
@@ -999,49 +999,49 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>부적합 사례</t>
+          <t>양식</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>부적합 보고서(NCR) 회신</t>
+          <t>시정조치 및 예방조치 관리대장 (QP-85-01-F01)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>004. CAPA 절차/004. 부적합/QP-85-01_부적합보고서_NCR_회신.pdf</t>
+          <t>004. CAPA 절차/002. 관련 양식/002. 시정조치 및 예방조치 요구, 보고서 관리 대장/QP-85-01-F01_시정조치_및_예방조치_관리대장.pdf</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>004. CAPA 절차/004. 부적합/QP-85-01_부적합보고서_NCR_회신.docx</t>
+          <t>004. CAPA 절차/002. 관련 양식/002. 시정조치 및 예방조치 요구, 보고서 관리 대장/QP-85-01-F01_시정조치_및_예방조치_관리대장.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>UDI 관리</t>
+          <t>CAPA</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>절차서</t>
+          <t>부적합 사례</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>UDI 절차서 (QP-758-01)</t>
+          <t>부적합 보고서(NCR) 회신</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>005. UDI 관리/001. 절차서/QP-758-01_UDI_절차서.pdf</t>
+          <t>004. CAPA 절차/004. 부적합/QP-85-01_부적합보고서_NCR_회신.pdf</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>005. UDI 관리/001. 절차서/QP-758-01_UDI_절차서.docx</t>
+          <t>004. CAPA 절차/004. 부적합/QP-85-01_부적합보고서_NCR_회신.docx</t>
         </is>
       </c>
     </row>
@@ -1053,22 +1053,22 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>양식</t>
+          <t>절차서</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>UDI 체계 수립 및 코드 생성 기록 (QP-758-01-F01)</t>
+          <t>UDI 절차서 (QP-758-01)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>005. UDI 관리/002. 관련 양식/001. UDI 체계 수립 및 코드 생성/QP-758-01-F01_UDI체계수립및코드생성기록.pdf</t>
+          <t>005. UDI 관리/001. 절차서/QP-758-01_UDI_절차서.pdf</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>005. UDI 관리/002. 관련 양식/001. UDI 체계 수립 및 코드 생성/QP-758-01-F01_UDI체계수립및코드생성기록.docx</t>
+          <t>005. UDI 관리/001. 절차서/QP-758-01_UDI_절차서.docx</t>
         </is>
       </c>
     </row>
@@ -1085,17 +1085,17 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>라벨링 및 포장 인쇄 적용 (QP-758-01-F02)</t>
+          <t>UDI 체계 수립 및 코드 생성 기록 (QP-758-01-F01)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>005. UDI 관리/002. 관련 양식/002. 라벨링 및 포장 인쇄 적용/QP-758-01-F02(마이크로카테터_UDI품질절차서_라벨링 및 포장인쇄).pdf</t>
+          <t>005. UDI 관리/002. 관련 양식/001. UDI 체계 수립 및 코드 생성/QP-758-01-F01_UDI체계수립및코드생성기록.pdf</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>005. UDI 관리/002. 관련 양식/002. 라벨링 및 포장 인쇄 적용/QP-758-01-F02(마이크로카테터_UDI품질절차서_라벨링 및 포장인쇄).docx</t>
+          <t>005. UDI 관리/002. 관련 양식/001. UDI 체계 수립 및 코드 생성/QP-758-01-F01_UDI체계수립및코드생성기록.docx</t>
         </is>
       </c>
     </row>
@@ -1112,15 +1112,42 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
+          <t>라벨링 및 포장 인쇄 적용 (QP-758-01-F02)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>005. UDI 관리/002. 관련 양식/002. 라벨링 및 포장 인쇄 적용/QP-758-01-F02(마이크로카테터_UDI품질절차서_라벨링 및 포장인쇄).pdf</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>005. UDI 관리/002. 관련 양식/002. 라벨링 및 포장 인쇄 적용/QP-758-01-F02(마이크로카테터_UDI품질절차서_라벨링 및 포장인쇄).docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>UDI 관리</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>양식</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
           <t>통합시스템 등록 및 추적관리 (QP-758-01-F03)</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>005. UDI 관리/002. 관련 양식/003. 통합시스템 등록 및 추적관리/QP-758-01-F03_작성예시_KMHSE-02-10.pdf</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>005. UDI 관리/002. 관련 양식/003. 통합시스템 등록 및 추적관리/QP-758-01-F03_작성예시_KMHSE-02-10.docx</t>
         </is>

--- a/data.xlsx
+++ b/data.xlsx
@@ -85,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -96,6 +96,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -462,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -489,56 +492,89 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>의료기기 QMS 절차서 교육 (임시)</t>
+          <t>RA Portfolio</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>메인 문구</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>의료기기 QMS
+절차서 교육</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>보조 문구</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>ISO 13485:2016을 바탕으로 작성한 5개 절차서의 양식, 영상, 시험을 분야별로 확인할 수 있습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>사용 안내</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>· 이 파일은 웹앱의 데이터입니다. 시트 이름과 1행(제목 행)은 바꾸지 마세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>· 분야 순서: 자료 시트에 처음 나오는 순서대로 웹앱 상단 탭이 만들어집니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>· 파일 경로: index.html이 있는 위치 기준이며, 폴더 구분은 / 를 사용합니다.</t>
+          <t>· 이 파일은 웹앱의 데이터입니다. 시트 이름과 1행(제목 행)은 바꾸지 마세요.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>· 보기파일(PDF)을 입력하면 웹에서 미리보기, 원본파일은 다운로드로 제공됩니다.</t>
+          <t>· 분야 순서: 자료 시트에 처음 나오는 순서대로 웹앱 상단 탭이 만들어집니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>· 시험문제 정답: 객관식은 정답 보기 번호(1~4), 주관식은 모범답안을 입력합니다.</t>
+          <t>· 파일 경로: index.html이 있는 위치 기준이며, 폴더 구분은 / 를 사용합니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>· 보기파일(PDF)을 입력하면 웹에서 미리보기, 원본파일은 다운로드로 제공됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>· 시험문제 정답: 객관식은 정답 보기 번호(1~4), 주관식은 모범답안을 입력합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>· 빈 행이나 분야가 비어 있는 행은 무시됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>· 메인 문구에서 줄을 바꾸려면 셀 안에서 Alt+Enter를 누르세요.</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자료" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시험문제" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참고자료" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="소개" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자료" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시험문제" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참고자료" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -85,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,6 +100,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -521,7 +525,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -575,6 +578,13 @@
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>· 메인 문구에서 줄을 바꾸려면 셀 안에서 Alt+Enter를 누르세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>· 소개 시트: 연결 분야를 비워 두면 맨 위 큰 항목(품목 선정 이유), 분야를 적으면 주제별 항목으로 표시됩니다. 본문 줄바꿈(Alt+Enter)은 문단으로 나뉩니다.</t>
         </is>
       </c>
     </row>
@@ -584,6 +594,188 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>연결 분야</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>품목 선정 이유</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>고위험 의료기기의 복잡한 규제 요구사항에 도전하며 RA 실무 역량을 폭넓게 학습하고자 마이크로카테터를 선정했습니다.</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>RA 업무를 처음 학습하면서 기본적인 의료기기부터 살펴보던 중, 고위험 등급에 해당하는 의료기기에 관심을 갖게 되었습니다.
+그 과정에서 4등급 마이크로카테터를 알게 되었으며, 높은 위험도를 가진 제품일수록 더욱 엄격한 안전성·성능 검증과 품질관리가 요구된다는 점에 주목했습니다.
+보다 복잡한 규제 요구사항을 직접 이해하고 적용하는 과정에서 RA 실무 역량을 폭넓게 키우고자 해당 품목을 선정했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>위험관리</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>위험 관리</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>의료기기 전 생애주기에서 발생할 수 있는 위험을 식별·평가·통제하여 환자의 안전을 확보하는 핵심 활동입니다.</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>의료기기는 의도한 성능을 발휘하는 것뿐만 아니라, 사용 과정에서 발생할 수 있는 위험을 허용 가능한 수준으로 관리하는 것이 중요하다고 생각했습니다.
+특히 인체 혈관 내에 사용되는 마이크로카테터는 기기 결함이나 사용상의 문제가 환자의 안전에 직접적인 영향을 미칠 수 있습니다.
+이에 의료기기의 전 생애주기에 걸쳐 위해요인을 식별하고 위험을 평가·통제하는 과정을 이해하고자 위험관리를 주요 학습 주제로 선정했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>공급업체관리</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>공급업체 관리</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>완제품의 품질은 제조 이전 단계부터 시작됩니다. 공급업체의 적격성을 평가하고 지속적으로 관리하는 과정에 주목했습니다.</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>의료기기의 품질은 최종 제품의 검사뿐만 아니라, 제조에 사용되는 원재료와 외부에서 제공받는 공정 및 서비스의 품질에 의해서도 결정된다고 생각했습니다.
+따라서 공급업체가 요구되는 품질 수준을 지속적으로 충족할 수 있는지 평가하고 관리하는 과정은 제품의 품질 확보를 위한 중요한 예방 활동입니다.
+이러한 관점에서 공급업체의 선정, 평가 및 지속적인 관리 체계를 이해하고자 해당 주제를 선정했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>멸균 공정 밸리데이션</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>멸균 공정 밸리데이션</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>환자의 감염 위험을 줄이기 위해 멸균 공정이 요구되는 멸균보증 수준을 일관되게 달성하는지 검증하는 과정입니다.</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>마이크로카테터는 인체 혈관 내에 삽입되는 의료기기로, 미생물 오염에 의한 감염 위험을 예방하기 위해 멸균 관리가 매우 중요합니다.
+특히 멸균 공정은 최종 제품의 검사만으로 모든 제품의 무균성을 보증하기 어려우므로, 사전에 공정의 유효성과 재현성을 검증하는 밸리데이션이 필수적입니다.
+이에 멸균 공정이 일관되게 요구되는 멸균보증 수준을 달성할 수 있음을 입증하는 과정을 이해하고자 해당 주제를 선정했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>CAPA(시정 및 예방조치)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>CAPA</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>의료기기의 품질 문제를 단순히 수정하는 데 그치지 않고, 근본 원인을 분석하여 재발과 잠재적 부적합을 예방하는 지속적인 품질개선 체계를 이해하고자 선정했습니다.</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>의료기기의 품질을 확보하기 위해서는 발생한 문제를 해결하는 것뿐만 아니라, 문제의 근본 원인을 파악하고 동일한 문제가 반복되지 않도록 관리하는 과정이 중요하다고 생각했습니다.
+CAPA는 발생한 부적합의 원인을 분석하여 재발을 방지하는 시정조치와 잠재적인 부적합의 원인을 사전에 제거하는 예방조치를 통해 의료기기의 품질경영시스템을 지속적으로 개선하는 활동입니다.
+이에 부적합의 식별부터 원인 분석, 시정 및 예방조치의 수립과 실행, 효과성 검증에 이르는 전반적인 절차를 이해하고, 의료기기의 품질과 안전성을 지속적으로 확보하는 방법을 학습하고자 해당 주제를 선정했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>UDI 관리</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>UDI 관리</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>의료기기의 식별과 추적성을 확보하기 위해 UDI의 생성부터 라벨 표시, 정보 등록 및 유통에 이르는 관리 체계를 이해하고자 선정했습니다.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>의료기기의 안전성과 품질을 확보하기 위해서는 제조 단계뿐만 아니라 유통 및 사용 이후까지 제품을 식별하고 추적할 수 있는 관리 체계가 중요하다고 생각했습니다.
+UDI는 의료기기에 고유한 식별정보를 부여하여 제품의 추적성을 확보하고, 문제 발생 시 신속한 제품 식별과 회수 등 효과적인 사후관리를 가능하게 하는 제도입니다.
+이에 UDI의 생성부터 라벨 표시, 정보 등록 및 유통에 이르는 전반적인 관리 절차를 이해하고, 의료기기의 전 생애주기에서 추적성이 어떻게 확보되는지 학습하고자 해당 주제를 선정했습니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1202,7 +1394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3378,7 +3570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -585,6 +585,20 @@
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>· 소개 시트: 연결 분야를 비워 두면 맨 위 큰 항목(품목 선정 이유), 분야를 적으면 주제별 항목으로 표시됩니다. 본문 줄바꿈(Alt+Enter)은 문단으로 나뉩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>· 참고자료 시트: 분야를 '공통'으로 적으면 상단 메뉴의 '참고자료' 페이지에 표시되고, 분야 이름을 적으면 해당 분야의 참고자료 탭에 표시됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>· 썸네일 칸은 비워 두면 자동(영상은 YouTube 썸네일, 사이트는 사이트 아이콘)이고, 저장소에 올린 이미지 경로를 적으면 그 이미지를 씁니다.</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3584,6 +3598,8 @@
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3612,6 +3628,16 @@
           <t>설명</t>
         </is>
       </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>썸네일</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -3639,6 +3665,8 @@
           <t>4.1.2 b) 품질경영시스템 프로세스의 위험 기반 접근, 7.1 제품실현 기획, 4.2.5 기록 관리 (제품 위험관리는 ISO 14971:2019 적용)</t>
         </is>
       </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -3666,6 +3694,8 @@
           <t>7.4.1 구매 프로세스, 7.4.2 구매 정보, 7.4.3 구매품 검증, 4.1.5 외부 위탁 프로세스</t>
         </is>
       </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3693,6 +3723,8 @@
           <t>7.5.7 멸균 공정 및 무균 차단 시스템 밸리데이션, 7.5.5 멸균 의료기기 특별 요구사항, 7.5.6 공정 밸리데이션</t>
         </is>
       </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3720,6 +3752,8 @@
           <t>8.5.2 시정조치, 8.5.3 예방조치, 8.3.3 인도 후 부적합 대응, 8.4 데이터 분석, 5.6.2 e) 경영검토 입력</t>
         </is>
       </c>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3747,6 +3781,174 @@
           <t>7.5.8 식별, 7.5.9.1 추적성, 4.2.5 기록 관리</t>
         </is>
       </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>웹사이트</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>의료기기안전정보원</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>https://www.nids.or.kr/</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>웹사이트</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>국가법령정보센터 의료기기법</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/%EB%B2%95%EB%A0%B9/%EC%9D%98%EB%A3%8C%EA%B8%B0%EA%B8%B0%EB%B2%95</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>법제처</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>웹사이트</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>의료기기전자민원시스템</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>https://emedi.mfds.go.kr/msismext/emd/min/mainView.do</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>동영상</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>의료기기 규제과학 전문가 중기과정이란</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-b8-i-5cD_s</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>의료기기안전정보원</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>동영상</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>2026 국제 의료기기 규제 포럼_호주 GMP·MDSAP 운영 현황 및 PMS와의 연계</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=okXIv7tw3hw</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>의료기기안전정보원</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>동영상</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>[아고라스쿨] 의료기기 인허가 프로세스에 대해서 알아보자!</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8_OJvxE6rOc</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>보건산업혁신창업센터 KBIC</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
